--- a/templates_docs/template_unloading.xlsx
+++ b/templates_docs/template_unloading.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\kp_generator\templates_docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vlasov\Desktop\Дела\kp_generator-main\templates_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03CA9B10-6CB0-4132-8695-41AE1643E46B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -53,11 +52,14 @@
   <si>
     <t>№</t>
   </si>
+  <si>
+    <t>Цена за кг</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -405,18 +407,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H120"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I120"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="29.7109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="23.7109375" style="2" customWidth="1"/>
-    <col min="4" max="8" width="15.28515625" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="2"/>
+    <col min="4" max="9" width="15.28515625" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -433,16 +435,19 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -453,8 +458,9 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -465,8 +471,9 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -477,8 +484,9 @@
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -489,8 +497,9 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -501,8 +510,9 @@
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -513,8 +523,9 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -525,8 +536,9 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -537,8 +549,9 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -549,8 +562,9 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -561,8 +575,9 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -573,8 +588,9 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -585,8 +601,9 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -597,8 +614,9 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
-    </row>
-    <row r="15" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -609,8 +627,9 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
-    </row>
-    <row r="16" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -621,8 +640,9 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -633,8 +653,9 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
-    </row>
-    <row r="18" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -645,8 +666,9 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
-    </row>
-    <row r="19" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -657,8 +679,9 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -669,8 +692,9 @@
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -681,8 +705,9 @@
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -693,8 +718,9 @@
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
-    </row>
-    <row r="23" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -705,8 +731,9 @@
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
-    </row>
-    <row r="24" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I23" s="3"/>
+    </row>
+    <row r="24" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -717,8 +744,9 @@
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
-    </row>
-    <row r="25" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I24" s="3"/>
+    </row>
+    <row r="25" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -729,8 +757,9 @@
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
-    </row>
-    <row r="26" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I25" s="3"/>
+    </row>
+    <row r="26" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -741,8 +770,9 @@
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
-    </row>
-    <row r="27" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I26" s="3"/>
+    </row>
+    <row r="27" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -753,8 +783,9 @@
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
-    </row>
-    <row r="28" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I27" s="3"/>
+    </row>
+    <row r="28" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -765,8 +796,9 @@
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
-    </row>
-    <row r="29" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I28" s="3"/>
+    </row>
+    <row r="29" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -777,8 +809,9 @@
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
-    </row>
-    <row r="30" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I29" s="3"/>
+    </row>
+    <row r="30" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -789,8 +822,9 @@
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
-    </row>
-    <row r="31" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I30" s="3"/>
+    </row>
+    <row r="31" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -801,8 +835,9 @@
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
-    </row>
-    <row r="32" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I31" s="3"/>
+    </row>
+    <row r="32" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -813,8 +848,9 @@
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
-    </row>
-    <row r="33" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I32" s="3"/>
+    </row>
+    <row r="33" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -825,8 +861,9 @@
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
-    </row>
-    <row r="34" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I33" s="3"/>
+    </row>
+    <row r="34" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -837,8 +874,9 @@
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
-    </row>
-    <row r="35" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I34" s="3"/>
+    </row>
+    <row r="35" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -849,8 +887,9 @@
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
-    </row>
-    <row r="36" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I35" s="3"/>
+    </row>
+    <row r="36" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -861,8 +900,9 @@
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
-    </row>
-    <row r="37" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I36" s="3"/>
+    </row>
+    <row r="37" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -873,8 +913,9 @@
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
-    </row>
-    <row r="38" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I37" s="3"/>
+    </row>
+    <row r="38" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -885,8 +926,9 @@
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
-    </row>
-    <row r="39" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I38" s="3"/>
+    </row>
+    <row r="39" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -897,8 +939,9 @@
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
-    </row>
-    <row r="40" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I39" s="3"/>
+    </row>
+    <row r="40" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -909,8 +952,9 @@
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
-    </row>
-    <row r="41" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I40" s="3"/>
+    </row>
+    <row r="41" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -921,8 +965,9 @@
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
-    </row>
-    <row r="42" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I41" s="3"/>
+    </row>
+    <row r="42" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -933,8 +978,9 @@
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
-    </row>
-    <row r="43" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I42" s="3"/>
+    </row>
+    <row r="43" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -945,8 +991,9 @@
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
-    </row>
-    <row r="44" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I43" s="3"/>
+    </row>
+    <row r="44" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -957,8 +1004,9 @@
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
-    </row>
-    <row r="45" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I44" s="3"/>
+    </row>
+    <row r="45" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -969,8 +1017,9 @@
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
-    </row>
-    <row r="46" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I45" s="3"/>
+    </row>
+    <row r="46" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -981,8 +1030,9 @@
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
-    </row>
-    <row r="47" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I46" s="3"/>
+    </row>
+    <row r="47" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -993,8 +1043,9 @@
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
-    </row>
-    <row r="48" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I47" s="3"/>
+    </row>
+    <row r="48" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -1005,8 +1056,9 @@
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
-    </row>
-    <row r="49" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I48" s="3"/>
+    </row>
+    <row r="49" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -1017,8 +1069,9 @@
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
-    </row>
-    <row r="50" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I49" s="3"/>
+    </row>
+    <row r="50" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -1029,8 +1082,9 @@
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
-    </row>
-    <row r="51" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I50" s="3"/>
+    </row>
+    <row r="51" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -1041,8 +1095,9 @@
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
-    </row>
-    <row r="52" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I51" s="3"/>
+    </row>
+    <row r="52" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -1053,8 +1108,9 @@
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
-    </row>
-    <row r="53" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I52" s="3"/>
+    </row>
+    <row r="53" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -1065,8 +1121,9 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
-    </row>
-    <row r="54" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I53" s="3"/>
+    </row>
+    <row r="54" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -1077,8 +1134,9 @@
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
-    </row>
-    <row r="55" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I54" s="3"/>
+    </row>
+    <row r="55" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -1089,8 +1147,9 @@
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
-    </row>
-    <row r="56" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I55" s="3"/>
+    </row>
+    <row r="56" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -1101,8 +1160,9 @@
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
-    </row>
-    <row r="57" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I56" s="3"/>
+    </row>
+    <row r="57" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -1113,8 +1173,9 @@
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
-    </row>
-    <row r="58" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I57" s="3"/>
+    </row>
+    <row r="58" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -1125,8 +1186,9 @@
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
-    </row>
-    <row r="59" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I58" s="3"/>
+    </row>
+    <row r="59" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -1137,8 +1199,9 @@
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
-    </row>
-    <row r="60" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I59" s="3"/>
+    </row>
+    <row r="60" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -1149,8 +1212,9 @@
       <c r="F60" s="3"/>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
-    </row>
-    <row r="61" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I60" s="3"/>
+    </row>
+    <row r="61" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -1161,8 +1225,9 @@
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
-    </row>
-    <row r="62" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I61" s="3"/>
+    </row>
+    <row r="62" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -1173,8 +1238,9 @@
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
-    </row>
-    <row r="63" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I62" s="3"/>
+    </row>
+    <row r="63" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -1185,8 +1251,9 @@
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
-    </row>
-    <row r="64" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I63" s="3"/>
+    </row>
+    <row r="64" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -1197,8 +1264,9 @@
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
-    </row>
-    <row r="65" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I64" s="3"/>
+    </row>
+    <row r="65" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -1209,8 +1277,9 @@
       <c r="F65" s="3"/>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
-    </row>
-    <row r="66" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I65" s="3"/>
+    </row>
+    <row r="66" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -1221,8 +1290,9 @@
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
-    </row>
-    <row r="67" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I66" s="3"/>
+    </row>
+    <row r="67" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -1233,8 +1303,9 @@
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
-    </row>
-    <row r="68" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I67" s="3"/>
+    </row>
+    <row r="68" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -1245,8 +1316,9 @@
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
       <c r="H68" s="3"/>
-    </row>
-    <row r="69" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I68" s="3"/>
+    </row>
+    <row r="69" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -1257,8 +1329,9 @@
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
       <c r="H69" s="3"/>
-    </row>
-    <row r="70" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I69" s="3"/>
+    </row>
+    <row r="70" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -1269,8 +1342,9 @@
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
-    </row>
-    <row r="71" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I70" s="3"/>
+    </row>
+    <row r="71" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -1281,8 +1355,9 @@
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
       <c r="H71" s="3"/>
-    </row>
-    <row r="72" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I71" s="3"/>
+    </row>
+    <row r="72" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>71</v>
       </c>
@@ -1293,8 +1368,9 @@
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
-    </row>
-    <row r="73" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I72" s="3"/>
+    </row>
+    <row r="73" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -1305,8 +1381,9 @@
       <c r="F73" s="3"/>
       <c r="G73" s="3"/>
       <c r="H73" s="3"/>
-    </row>
-    <row r="74" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I73" s="3"/>
+    </row>
+    <row r="74" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -1317,8 +1394,9 @@
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
-    </row>
-    <row r="75" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I74" s="3"/>
+    </row>
+    <row r="75" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -1329,8 +1407,9 @@
       <c r="F75" s="3"/>
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
-    </row>
-    <row r="76" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I75" s="3"/>
+    </row>
+    <row r="76" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -1341,8 +1420,9 @@
       <c r="F76" s="3"/>
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
-    </row>
-    <row r="77" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I76" s="3"/>
+    </row>
+    <row r="77" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -1353,8 +1433,9 @@
       <c r="F77" s="3"/>
       <c r="G77" s="3"/>
       <c r="H77" s="3"/>
-    </row>
-    <row r="78" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I77" s="3"/>
+    </row>
+    <row r="78" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -1365,8 +1446,9 @@
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
-    </row>
-    <row r="79" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I78" s="3"/>
+    </row>
+    <row r="79" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -1377,8 +1459,9 @@
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
       <c r="H79" s="3"/>
-    </row>
-    <row r="80" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I79" s="3"/>
+    </row>
+    <row r="80" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -1389,8 +1472,9 @@
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
       <c r="H80" s="3"/>
-    </row>
-    <row r="81" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I80" s="3"/>
+    </row>
+    <row r="81" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -1401,8 +1485,9 @@
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
       <c r="H81" s="3"/>
-    </row>
-    <row r="82" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I81" s="3"/>
+    </row>
+    <row r="82" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -1413,8 +1498,9 @@
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
       <c r="H82" s="3"/>
-    </row>
-    <row r="83" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I82" s="3"/>
+    </row>
+    <row r="83" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -1425,8 +1511,9 @@
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
       <c r="H83" s="3"/>
-    </row>
-    <row r="84" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I83" s="3"/>
+    </row>
+    <row r="84" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -1437,8 +1524,9 @@
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
       <c r="H84" s="3"/>
-    </row>
-    <row r="85" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I84" s="3"/>
+    </row>
+    <row r="85" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -1449,8 +1537,9 @@
       <c r="F85" s="3"/>
       <c r="G85" s="3"/>
       <c r="H85" s="3"/>
-    </row>
-    <row r="86" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I85" s="3"/>
+    </row>
+    <row r="86" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -1461,8 +1550,9 @@
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
       <c r="H86" s="3"/>
-    </row>
-    <row r="87" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I86" s="3"/>
+    </row>
+    <row r="87" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>86</v>
       </c>
@@ -1473,8 +1563,9 @@
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
       <c r="H87" s="3"/>
-    </row>
-    <row r="88" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I87" s="3"/>
+    </row>
+    <row r="88" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>87</v>
       </c>
@@ -1485,8 +1576,9 @@
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
       <c r="H88" s="3"/>
-    </row>
-    <row r="89" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I88" s="3"/>
+    </row>
+    <row r="89" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -1497,8 +1589,9 @@
       <c r="F89" s="3"/>
       <c r="G89" s="3"/>
       <c r="H89" s="3"/>
-    </row>
-    <row r="90" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I89" s="3"/>
+    </row>
+    <row r="90" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -1509,8 +1602,9 @@
       <c r="F90" s="3"/>
       <c r="G90" s="3"/>
       <c r="H90" s="3"/>
-    </row>
-    <row r="91" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I90" s="3"/>
+    </row>
+    <row r="91" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>90</v>
       </c>
@@ -1521,8 +1615,9 @@
       <c r="F91" s="3"/>
       <c r="G91" s="3"/>
       <c r="H91" s="3"/>
-    </row>
-    <row r="92" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I91" s="3"/>
+    </row>
+    <row r="92" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>91</v>
       </c>
@@ -1533,8 +1628,9 @@
       <c r="F92" s="3"/>
       <c r="G92" s="3"/>
       <c r="H92" s="3"/>
-    </row>
-    <row r="93" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I92" s="3"/>
+    </row>
+    <row r="93" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>92</v>
       </c>
@@ -1545,8 +1641,9 @@
       <c r="F93" s="3"/>
       <c r="G93" s="3"/>
       <c r="H93" s="3"/>
-    </row>
-    <row r="94" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I93" s="3"/>
+    </row>
+    <row r="94" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>93</v>
       </c>
@@ -1557,8 +1654,9 @@
       <c r="F94" s="3"/>
       <c r="G94" s="3"/>
       <c r="H94" s="3"/>
-    </row>
-    <row r="95" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I94" s="3"/>
+    </row>
+    <row r="95" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>94</v>
       </c>
@@ -1569,8 +1667,9 @@
       <c r="F95" s="3"/>
       <c r="G95" s="3"/>
       <c r="H95" s="3"/>
-    </row>
-    <row r="96" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I95" s="3"/>
+    </row>
+    <row r="96" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>95</v>
       </c>
@@ -1581,8 +1680,9 @@
       <c r="F96" s="3"/>
       <c r="G96" s="3"/>
       <c r="H96" s="3"/>
-    </row>
-    <row r="97" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I96" s="3"/>
+    </row>
+    <row r="97" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -1593,8 +1693,9 @@
       <c r="F97" s="3"/>
       <c r="G97" s="3"/>
       <c r="H97" s="3"/>
-    </row>
-    <row r="98" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I97" s="3"/>
+    </row>
+    <row r="98" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>97</v>
       </c>
@@ -1605,8 +1706,9 @@
       <c r="F98" s="3"/>
       <c r="G98" s="3"/>
       <c r="H98" s="3"/>
-    </row>
-    <row r="99" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I98" s="3"/>
+    </row>
+    <row r="99" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>98</v>
       </c>
@@ -1617,8 +1719,9 @@
       <c r="F99" s="3"/>
       <c r="G99" s="3"/>
       <c r="H99" s="3"/>
-    </row>
-    <row r="100" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I99" s="3"/>
+    </row>
+    <row r="100" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -1629,8 +1732,9 @@
       <c r="F100" s="3"/>
       <c r="G100" s="3"/>
       <c r="H100" s="3"/>
-    </row>
-    <row r="101" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I100" s="3"/>
+    </row>
+    <row r="101" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -1641,8 +1745,9 @@
       <c r="F101" s="3"/>
       <c r="G101" s="3"/>
       <c r="H101" s="3"/>
-    </row>
-    <row r="102" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I101" s="3"/>
+    </row>
+    <row r="102" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>101</v>
       </c>
@@ -1653,8 +1758,9 @@
       <c r="F102" s="3"/>
       <c r="G102" s="3"/>
       <c r="H102" s="3"/>
-    </row>
-    <row r="103" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I102" s="3"/>
+    </row>
+    <row r="103" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>102</v>
       </c>
@@ -1665,8 +1771,9 @@
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
-    </row>
-    <row r="104" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I103" s="3"/>
+    </row>
+    <row r="104" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -1677,8 +1784,9 @@
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
-    </row>
-    <row r="105" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I104" s="3"/>
+    </row>
+    <row r="105" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>104</v>
       </c>
@@ -1689,8 +1797,9 @@
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
-    </row>
-    <row r="106" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I105" s="3"/>
+    </row>
+    <row r="106" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>105</v>
       </c>
@@ -1701,8 +1810,9 @@
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
-    </row>
-    <row r="107" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I106" s="3"/>
+    </row>
+    <row r="107" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -1713,8 +1823,9 @@
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
-    </row>
-    <row r="108" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I107" s="3"/>
+    </row>
+    <row r="108" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>107</v>
       </c>
@@ -1725,8 +1836,9 @@
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
       <c r="H108" s="3"/>
-    </row>
-    <row r="109" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I108" s="3"/>
+    </row>
+    <row r="109" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -1737,8 +1849,9 @@
       <c r="F109" s="3"/>
       <c r="G109" s="3"/>
       <c r="H109" s="3"/>
-    </row>
-    <row r="110" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I109" s="3"/>
+    </row>
+    <row r="110" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -1749,8 +1862,9 @@
       <c r="F110" s="3"/>
       <c r="G110" s="3"/>
       <c r="H110" s="3"/>
-    </row>
-    <row r="111" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I110" s="3"/>
+    </row>
+    <row r="111" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -1761,8 +1875,9 @@
       <c r="F111" s="3"/>
       <c r="G111" s="3"/>
       <c r="H111" s="3"/>
-    </row>
-    <row r="112" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I111" s="3"/>
+    </row>
+    <row r="112" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -1773,8 +1888,9 @@
       <c r="F112" s="3"/>
       <c r="G112" s="3"/>
       <c r="H112" s="3"/>
-    </row>
-    <row r="113" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I112" s="3"/>
+    </row>
+    <row r="113" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -1785,8 +1901,9 @@
       <c r="F113" s="3"/>
       <c r="G113" s="3"/>
       <c r="H113" s="3"/>
-    </row>
-    <row r="114" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I113" s="3"/>
+    </row>
+    <row r="114" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
         <v>113</v>
       </c>
@@ -1797,8 +1914,9 @@
       <c r="F114" s="3"/>
       <c r="G114" s="3"/>
       <c r="H114" s="3"/>
-    </row>
-    <row r="115" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I114" s="3"/>
+    </row>
+    <row r="115" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
         <v>114</v>
       </c>
@@ -1809,8 +1927,9 @@
       <c r="F115" s="3"/>
       <c r="G115" s="3"/>
       <c r="H115" s="3"/>
-    </row>
-    <row r="116" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I115" s="3"/>
+    </row>
+    <row r="116" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
         <v>115</v>
       </c>
@@ -1821,8 +1940,9 @@
       <c r="F116" s="3"/>
       <c r="G116" s="3"/>
       <c r="H116" s="3"/>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I116" s="3"/>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
         <v>116</v>
       </c>
@@ -1833,8 +1953,9 @@
       <c r="F117" s="3"/>
       <c r="G117" s="3"/>
       <c r="H117" s="3"/>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I117" s="3"/>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
         <v>117</v>
       </c>
@@ -1845,8 +1966,9 @@
       <c r="F118" s="3"/>
       <c r="G118" s="3"/>
       <c r="H118" s="3"/>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I118" s="3"/>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
         <v>118</v>
       </c>
@@ -1857,8 +1979,9 @@
       <c r="F119" s="3"/>
       <c r="G119" s="3"/>
       <c r="H119" s="3"/>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I119" s="3"/>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
         <v>119</v>
       </c>
@@ -1869,6 +1992,7 @@
       <c r="F120" s="3"/>
       <c r="G120" s="3"/>
       <c r="H120" s="3"/>
+      <c r="I120" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/templates_docs/template_unloading.xlsx
+++ b/templates_docs/template_unloading.xlsx
@@ -408,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I120"/>
+  <dimension ref="A1:K122"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="2" customWidth="1"/>
@@ -1682,7 +1682,7 @@
       <c r="H96" s="3"/>
       <c r="I96" s="3"/>
     </row>
-    <row r="97" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -1695,7 +1695,7 @@
       <c r="H97" s="3"/>
       <c r="I97" s="3"/>
     </row>
-    <row r="98" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>97</v>
       </c>
@@ -1708,7 +1708,7 @@
       <c r="H98" s="3"/>
       <c r="I98" s="3"/>
     </row>
-    <row r="99" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>98</v>
       </c>
@@ -1721,7 +1721,7 @@
       <c r="H99" s="3"/>
       <c r="I99" s="3"/>
     </row>
-    <row r="100" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -1734,7 +1734,7 @@
       <c r="H100" s="3"/>
       <c r="I100" s="3"/>
     </row>
-    <row r="101" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -1747,252 +1747,278 @@
       <c r="H101" s="3"/>
       <c r="I101" s="3"/>
     </row>
-    <row r="102" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="3">
-        <v>101</v>
-      </c>
-      <c r="B102" s="3"/>
-      <c r="C102" s="3"/>
-      <c r="D102" s="3"/>
-      <c r="E102" s="3"/>
-      <c r="F102" s="3"/>
-      <c r="G102" s="3"/>
-      <c r="H102" s="3"/>
-      <c r="I102" s="3"/>
-    </row>
-    <row r="103" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="3">
-        <v>102</v>
-      </c>
-      <c r="B103" s="3"/>
-      <c r="C103" s="3"/>
-      <c r="D103" s="3"/>
-      <c r="E103" s="3"/>
-      <c r="F103" s="3"/>
-      <c r="G103" s="3"/>
-      <c r="H103" s="3"/>
-      <c r="I103" s="3"/>
-    </row>
-    <row r="104" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="3">
-        <v>103</v>
-      </c>
-      <c r="B104" s="3"/>
-      <c r="C104" s="3"/>
-      <c r="D104" s="3"/>
-      <c r="E104" s="3"/>
-      <c r="F104" s="3"/>
-      <c r="G104" s="3"/>
-      <c r="H104" s="3"/>
-      <c r="I104" s="3"/>
-    </row>
-    <row r="105" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="3">
-        <v>104</v>
-      </c>
-      <c r="B105" s="3"/>
-      <c r="C105" s="3"/>
-      <c r="D105" s="3"/>
-      <c r="E105" s="3"/>
-      <c r="F105" s="3"/>
-      <c r="G105" s="3"/>
-      <c r="H105" s="3"/>
-      <c r="I105" s="3"/>
-    </row>
-    <row r="106" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="3">
-        <v>105</v>
-      </c>
-      <c r="B106" s="3"/>
-      <c r="C106" s="3"/>
-      <c r="D106" s="3"/>
-      <c r="E106" s="3"/>
-      <c r="F106" s="3"/>
-      <c r="G106" s="3"/>
-      <c r="H106" s="3"/>
-      <c r="I106" s="3"/>
-    </row>
-    <row r="107" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="3">
-        <v>106</v>
-      </c>
-      <c r="B107" s="3"/>
-      <c r="C107" s="3"/>
-      <c r="D107" s="3"/>
-      <c r="E107" s="3"/>
-      <c r="F107" s="3"/>
-      <c r="G107" s="3"/>
-      <c r="H107" s="3"/>
-      <c r="I107" s="3"/>
-    </row>
-    <row r="108" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="3">
-        <v>107</v>
-      </c>
-      <c r="B108" s="3"/>
-      <c r="C108" s="3"/>
-      <c r="D108" s="3"/>
-      <c r="E108" s="3"/>
-      <c r="F108" s="3"/>
-      <c r="G108" s="3"/>
-      <c r="H108" s="3"/>
-      <c r="I108" s="3"/>
-    </row>
-    <row r="109" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="3">
-        <v>108</v>
-      </c>
-      <c r="B109" s="3"/>
-      <c r="C109" s="3"/>
-      <c r="D109" s="3"/>
-      <c r="E109" s="3"/>
-      <c r="F109" s="3"/>
-      <c r="G109" s="3"/>
-      <c r="H109" s="3"/>
-      <c r="I109" s="3"/>
-    </row>
-    <row r="110" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="3">
-        <v>109</v>
-      </c>
-      <c r="B110" s="3"/>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3"/>
-      <c r="E110" s="3"/>
-      <c r="F110" s="3"/>
-      <c r="G110" s="3"/>
-      <c r="H110" s="3"/>
-      <c r="I110" s="3"/>
-    </row>
-    <row r="111" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="3">
-        <v>110</v>
-      </c>
-      <c r="B111" s="3"/>
-      <c r="C111" s="3"/>
-      <c r="D111" s="3"/>
-      <c r="E111" s="3"/>
-      <c r="F111" s="3"/>
-      <c r="G111" s="3"/>
-      <c r="H111" s="3"/>
-      <c r="I111" s="3"/>
-    </row>
-    <row r="112" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="3">
-        <v>111</v>
-      </c>
-      <c r="B112" s="3"/>
-      <c r="C112" s="3"/>
-      <c r="D112" s="3"/>
-      <c r="E112" s="3"/>
-      <c r="F112" s="3"/>
-      <c r="G112" s="3"/>
-      <c r="H112" s="3"/>
-      <c r="I112" s="3"/>
-    </row>
-    <row r="113" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="3">
-        <v>112</v>
-      </c>
-      <c r="B113" s="3"/>
-      <c r="C113" s="3"/>
-      <c r="D113" s="3"/>
-      <c r="E113" s="3"/>
-      <c r="F113" s="3"/>
-      <c r="G113" s="3"/>
-      <c r="H113" s="3"/>
-      <c r="I113" s="3"/>
-    </row>
-    <row r="114" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="3">
-        <v>113</v>
-      </c>
-      <c r="B114" s="3"/>
-      <c r="C114" s="3"/>
-      <c r="D114" s="3"/>
-      <c r="E114" s="3"/>
-      <c r="F114" s="3"/>
-      <c r="G114" s="3"/>
-      <c r="H114" s="3"/>
-      <c r="I114" s="3"/>
-    </row>
-    <row r="115" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="3">
-        <v>114</v>
-      </c>
-      <c r="B115" s="3"/>
-      <c r="C115" s="3"/>
-      <c r="D115" s="3"/>
-      <c r="E115" s="3"/>
-      <c r="F115" s="3"/>
-      <c r="G115" s="3"/>
-      <c r="H115" s="3"/>
-      <c r="I115" s="3"/>
-    </row>
-    <row r="116" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="3">
-        <v>115</v>
-      </c>
-      <c r="B116" s="3"/>
-      <c r="C116" s="3"/>
-      <c r="D116" s="3"/>
-      <c r="E116" s="3"/>
-      <c r="F116" s="3"/>
-      <c r="G116" s="3"/>
-      <c r="H116" s="3"/>
-      <c r="I116" s="3"/>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="3">
-        <v>116</v>
-      </c>
-      <c r="B117" s="3"/>
-      <c r="C117" s="3"/>
-      <c r="D117" s="3"/>
-      <c r="E117" s="3"/>
-      <c r="F117" s="3"/>
-      <c r="G117" s="3"/>
-      <c r="H117" s="3"/>
-      <c r="I117" s="3"/>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118" s="3">
-        <v>117</v>
-      </c>
-      <c r="B118" s="3"/>
-      <c r="C118" s="3"/>
-      <c r="D118" s="3"/>
-      <c r="E118" s="3"/>
-      <c r="F118" s="3"/>
-      <c r="G118" s="3"/>
-      <c r="H118" s="3"/>
-      <c r="I118" s="3"/>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A119" s="3">
-        <v>118</v>
-      </c>
-      <c r="B119" s="3"/>
-      <c r="C119" s="3"/>
-      <c r="D119" s="3"/>
-      <c r="E119" s="3"/>
-      <c r="F119" s="3"/>
-      <c r="G119" s="3"/>
-      <c r="H119" s="3"/>
-      <c r="I119" s="3"/>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120" s="3">
-        <v>119</v>
-      </c>
-      <c r="B120" s="3"/>
-      <c r="C120" s="3"/>
-      <c r="D120" s="3"/>
-      <c r="E120" s="3"/>
-      <c r="F120" s="3"/>
-      <c r="G120" s="3"/>
-      <c r="H120" s="3"/>
-      <c r="I120" s="3"/>
+    <row r="102" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102"/>
+      <c r="B102"/>
+      <c r="C102"/>
+      <c r="D102"/>
+      <c r="E102"/>
+      <c r="F102"/>
+      <c r="G102"/>
+      <c r="H102"/>
+      <c r="I102"/>
+      <c r="J102"/>
+      <c r="K102"/>
+    </row>
+    <row r="103" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103"/>
+      <c r="B103"/>
+      <c r="C103"/>
+      <c r="D103"/>
+      <c r="E103"/>
+      <c r="F103"/>
+      <c r="G103"/>
+      <c r="H103"/>
+      <c r="I103"/>
+      <c r="J103"/>
+      <c r="K103"/>
+    </row>
+    <row r="104" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104"/>
+      <c r="B104"/>
+      <c r="C104"/>
+      <c r="D104"/>
+      <c r="E104"/>
+      <c r="F104"/>
+      <c r="G104"/>
+      <c r="H104"/>
+      <c r="I104"/>
+      <c r="J104"/>
+      <c r="K104"/>
+    </row>
+    <row r="105" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105"/>
+      <c r="B105"/>
+      <c r="C105"/>
+      <c r="D105"/>
+      <c r="E105"/>
+      <c r="F105"/>
+      <c r="G105"/>
+      <c r="H105"/>
+      <c r="I105"/>
+      <c r="J105"/>
+      <c r="K105"/>
+    </row>
+    <row r="106" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106"/>
+      <c r="B106"/>
+      <c r="C106"/>
+      <c r="D106"/>
+      <c r="E106"/>
+      <c r="F106"/>
+      <c r="G106"/>
+      <c r="H106"/>
+      <c r="I106"/>
+      <c r="J106"/>
+      <c r="K106"/>
+    </row>
+    <row r="107" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107"/>
+      <c r="B107"/>
+      <c r="C107"/>
+      <c r="D107"/>
+      <c r="E107"/>
+      <c r="F107"/>
+      <c r="G107"/>
+      <c r="H107"/>
+      <c r="I107"/>
+      <c r="J107"/>
+      <c r="K107"/>
+    </row>
+    <row r="108" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108"/>
+      <c r="B108"/>
+      <c r="C108"/>
+      <c r="D108"/>
+      <c r="E108"/>
+      <c r="F108"/>
+      <c r="G108"/>
+      <c r="H108"/>
+      <c r="I108"/>
+      <c r="J108"/>
+      <c r="K108"/>
+    </row>
+    <row r="109" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109"/>
+      <c r="B109"/>
+      <c r="C109"/>
+      <c r="D109"/>
+      <c r="E109"/>
+      <c r="F109"/>
+      <c r="G109"/>
+      <c r="H109"/>
+      <c r="I109"/>
+      <c r="J109"/>
+      <c r="K109"/>
+    </row>
+    <row r="110" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110"/>
+      <c r="B110"/>
+      <c r="C110"/>
+      <c r="D110"/>
+      <c r="E110"/>
+      <c r="F110"/>
+      <c r="G110"/>
+      <c r="H110"/>
+      <c r="I110"/>
+      <c r="J110"/>
+      <c r="K110"/>
+    </row>
+    <row r="111" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111"/>
+      <c r="B111"/>
+      <c r="C111"/>
+      <c r="D111"/>
+      <c r="E111"/>
+      <c r="F111"/>
+      <c r="G111"/>
+      <c r="H111"/>
+      <c r="I111"/>
+      <c r="J111"/>
+      <c r="K111"/>
+    </row>
+    <row r="112" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112"/>
+      <c r="B112"/>
+      <c r="C112"/>
+      <c r="D112"/>
+      <c r="E112"/>
+      <c r="F112"/>
+      <c r="G112"/>
+      <c r="H112"/>
+      <c r="I112"/>
+      <c r="J112"/>
+      <c r="K112"/>
+    </row>
+    <row r="113" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113"/>
+      <c r="B113"/>
+      <c r="C113"/>
+      <c r="D113"/>
+      <c r="E113"/>
+      <c r="F113"/>
+      <c r="G113"/>
+      <c r="H113"/>
+      <c r="I113"/>
+      <c r="J113"/>
+      <c r="K113"/>
+    </row>
+    <row r="114" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114"/>
+      <c r="B114"/>
+      <c r="C114"/>
+      <c r="D114"/>
+      <c r="E114"/>
+      <c r="F114"/>
+      <c r="G114"/>
+      <c r="H114"/>
+      <c r="I114"/>
+      <c r="J114"/>
+      <c r="K114"/>
+    </row>
+    <row r="115" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115"/>
+      <c r="B115"/>
+      <c r="C115"/>
+      <c r="D115"/>
+      <c r="E115"/>
+      <c r="F115"/>
+      <c r="G115"/>
+      <c r="H115"/>
+      <c r="I115"/>
+      <c r="J115"/>
+      <c r="K115"/>
+    </row>
+    <row r="116" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116"/>
+      <c r="B116"/>
+      <c r="C116"/>
+      <c r="D116"/>
+      <c r="E116"/>
+      <c r="F116"/>
+      <c r="G116"/>
+      <c r="H116"/>
+      <c r="I116"/>
+      <c r="J116"/>
+      <c r="K116"/>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A117"/>
+      <c r="B117"/>
+      <c r="C117"/>
+      <c r="D117"/>
+      <c r="E117"/>
+      <c r="F117"/>
+      <c r="G117"/>
+      <c r="H117"/>
+      <c r="I117"/>
+      <c r="J117"/>
+      <c r="K117"/>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A118"/>
+      <c r="B118"/>
+      <c r="C118"/>
+      <c r="D118"/>
+      <c r="E118"/>
+      <c r="F118"/>
+      <c r="G118"/>
+      <c r="H118"/>
+      <c r="I118"/>
+      <c r="J118"/>
+      <c r="K118"/>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A119"/>
+      <c r="B119"/>
+      <c r="C119"/>
+      <c r="D119"/>
+      <c r="E119"/>
+      <c r="F119"/>
+      <c r="G119"/>
+      <c r="H119"/>
+      <c r="I119"/>
+      <c r="J119"/>
+      <c r="K119"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A120"/>
+      <c r="B120"/>
+      <c r="C120"/>
+      <c r="D120"/>
+      <c r="E120"/>
+      <c r="F120"/>
+      <c r="G120"/>
+      <c r="H120"/>
+      <c r="I120"/>
+      <c r="J120"/>
+      <c r="K120"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A121"/>
+      <c r="B121"/>
+      <c r="C121"/>
+      <c r="D121"/>
+      <c r="E121"/>
+      <c r="F121"/>
+      <c r="G121"/>
+      <c r="H121"/>
+      <c r="I121"/>
+      <c r="J121"/>
+      <c r="K121"/>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A122"/>
+      <c r="B122"/>
+      <c r="C122"/>
+      <c r="D122"/>
+      <c r="E122"/>
+      <c r="F122"/>
+      <c r="G122"/>
+      <c r="H122"/>
+      <c r="I122"/>
+      <c r="J122"/>
+      <c r="K122"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/templates_docs/template_unloading.xlsx
+++ b/templates_docs/template_unloading.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vlasov\Desktop\Дела\kp_generator-main\templates_docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vlasov\Desktop\Дела\kp_generator\templates_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
